--- a/i_test/test_D6_Tabella_1_fasciaeta_2025/g_output/D6_Table_1_85+.xlsx
+++ b/i_test/test_D6_Tabella_1_fasciaeta_2025/g_output/D6_Table_1_85+.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,6 +375,11 @@
           <t>SE</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Tutte</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -397,6 +402,11 @@
           <t>SE</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Tutte</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -411,12 +421,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>541</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1666</t>
         </is>
       </c>
     </row>
@@ -428,17 +443,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>289 (50,3%)</t>
+          <t>264 (46,0%)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>264 (48,6%)</t>
+          <t>259 (47,9%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>256 (46,6%)</t>
+          <t>286 (51,9%)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>809 (48,6%)</t>
         </is>
       </c>
     </row>
@@ -450,17 +470,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>51 (8,9%)</t>
+          <t>40 (7,0%)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50 (9,2%)</t>
+          <t>51 (9,4%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>57 (10,4%)</t>
+          <t>42 (7,6%)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>133 (8,0%)</t>
         </is>
       </c>
     </row>
@@ -474,110 +499,135 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A10BK</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>153 (26,7%)</t>
+          <t>A10BH 221 (0,4%)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>181 (33,3%)</t>
+          <t>A10BD08 215 (0,4%)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>190 (34,6%)</t>
+          <t>A10BD11 208 (0,4%)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>A10BH 617 (0,4%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A10BD13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>172 (30,0%)</t>
+          <t>A10BD21 220 (0,4%)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>189 (34,8%)</t>
+          <t>A10BJ 204 (0,4%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>160 (29,1%)</t>
+          <t>A10BD10 208 (0,4%)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>A10BD16 604 (0,4%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A10BJ</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>183 (31,9%)</t>
+          <t>A10AE54 212 (0,4%)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>152 (28,0%)</t>
+          <t>A10BD15 204 (0,4%)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>164 (29,9%)</t>
+          <t>A10BD20 207 (0,4%)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>A10BD11 593 (0,4%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A10BD09</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>162 (28,2%)</t>
+          <t>A10BD16 204 (0,4%)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>164 (30,2%)</t>
+          <t>A10BD16 200 (0,4%)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>173 (31,5%)</t>
+          <t>A10BD09 203 (0,4%)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>A10BD10 592 (0,4%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A10AE54</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>159 (27,7%)</t>
+          <t>A10BJ 203 (0,4%)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>157 (28,9%)</t>
+          <t>A10BD10 198 (0,4%)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>179 (32,6%)</t>
+          <t>A10BH 202 (0,4%)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>A10BD21 589 (0,4%)</t>
         </is>
       </c>
     </row>
@@ -596,17 +646,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>265 (46,2%)</t>
+          <t>1 (0,2%)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>257 (47,3%)</t>
+          <t>8 (1,5%)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>268 (48,8%)</t>
+          <t>4 (0,7%)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>13 (0,8%)</t>
         </is>
       </c>
     </row>
@@ -625,17 +680,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>403 (70,2%)</t>
+          <t>346 (60,3%)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>395 (72,7%)</t>
+          <t>339 (62,7%)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>400 (72,9%)</t>
+          <t>338 (61,3%)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.023 (61,4%)</t>
         </is>
       </c>
     </row>
@@ -647,17 +707,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>382 (66,6%)</t>
+          <t>48 (8,4%)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>377 (69,4%)</t>
+          <t>61 (11,3%)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>374 (68,1%)</t>
+          <t>42 (7,6%)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>151 (9,1%)</t>
         </is>
       </c>
     </row>
@@ -669,17 +734,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>131 (22,8%)</t>
+          <t>373 (65,0%)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>128 (23,6%)</t>
+          <t>372 (68,8%)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>136 (24,8%)</t>
+          <t>343 (62,3%)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.088 (65,3%)</t>
         </is>
       </c>
     </row>
@@ -691,17 +761,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>333 (58,0%)</t>
+          <t>252 (43,9%)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>315 (58,0%)</t>
+          <t>250 (46,2%)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>309 (56,3%)</t>
+          <t>242 (43,9%)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>744 (44,7%)</t>
         </is>
       </c>
     </row>

--- a/i_test/test_D6_Tabella_1_fasciaeta_2025/g_output/D6_Table_1_85+.xlsx
+++ b/i_test/test_D6_Tabella_1_fasciaeta_2025/g_output/D6_Table_1_85+.xlsx
@@ -504,22 +504,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A10BH 221 (0,4%)</t>
+          <t>NA 221 (38,5%)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A10BD08 215 (0,4%)</t>
+          <t>ll 215 (39,7%)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A10BD11 208 (0,4%)</t>
+          <t>ii 208 (37,7%)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>A10BH 617 (0,4%)</t>
+          <t>NA 617 (37,0%)</t>
         </is>
       </c>
     </row>
@@ -531,22 +531,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A10BD21 220 (0,4%)</t>
+          <t>ff 220 (38,3%)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A10BJ 204 (0,4%)</t>
+          <t>NA 204 (37,7%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A10BD10 208 (0,4%)</t>
+          <t>jj 208 (37,7%)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>A10BD16 604 (0,4%)</t>
+          <t>pp 604 (36,3%)</t>
         </is>
       </c>
     </row>
@@ -558,22 +558,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A10AE54 212 (0,4%)</t>
+          <t>oo 212 (36,9%)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A10BD15 204 (0,4%)</t>
+          <t>qq 204 (37,7%)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A10BD20 207 (0,4%)</t>
+          <t>rr 207 (37,6%)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>A10BD11 593 (0,4%)</t>
+          <t>ii 593 (35,6%)</t>
         </is>
       </c>
     </row>
@@ -585,22 +585,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A10BD16 204 (0,4%)</t>
+          <t>pp 204 (35,5%)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A10BD16 200 (0,4%)</t>
+          <t>pp 200 (37,0%)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A10BD09 203 (0,4%)</t>
+          <t>mm 203 (36,8%)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>A10BD10 592 (0,4%)</t>
+          <t>jj 592 (35,5%)</t>
         </is>
       </c>
     </row>
@@ -612,22 +612,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A10BJ 203 (0,4%)</t>
+          <t>NA 203 (35,4%)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A10BD10 198 (0,4%)</t>
+          <t>jj 198 (36,6%)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A10BH 202 (0,4%)</t>
+          <t>NA 202 (36,7%)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>A10BD21 589 (0,4%)</t>
+          <t>ff 589 (35,4%)</t>
         </is>
       </c>
     </row>
